--- a/docs/Funktionsliste.xlsx
+++ b/docs/Funktionsliste.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>"Tests für alle setzen": gleiche Auswahl für alle Kinder der aktuellen Ansicht (nach Filter und Suche) in einem Schritt.</t>
+          <t>"Tests für alle setzen": Fenster mit allen Kindern der KPF, in dem individuell per Kästchen bestimmt wird, für wen die gewählten Tests in einem Schritt gesetzt werden (mit Suche, Alle/Keine).</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
